--- a/inputs_qmd/tabla_glosario.xlsx
+++ b/inputs_qmd/tabla_glosario.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://educacionpublica-my.sharepoint.com/personal/alonso_arrano_dep_cl/Documents/2024/SAE - Anotate en la lista/reporteria_ael/inputs_qmd/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="22" documentId="11_AD4D2F04E46CFB4ACB3E20CA8550FF6C693EDF25" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CA7A02F7-1A9B-4762-9DAD-AE0BED92996B}"/>
+  <xr:revisionPtr revIDLastSave="26" documentId="11_AD4D2F04E46CFB4ACB3E20CA8550FF6C693EDF25" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CF3F47E7-2DC6-4C0B-B8F8-8CBC7DF71D9C}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -42,19 +42,19 @@
     <t>Proporción de EE que se encuentran al día con la gestión de AEL sobre el total de EE del SLEP.</t>
   </si>
   <si>
-    <t>Corresponde a la cantidad de estudiantes que no se les ha asignado una vacante aún cuando dicha vacante se encuentra disponible.</t>
-  </si>
-  <si>
-    <t>Corresponde a la cantidad de días transcurridos desde la última asignación de vacantes hasta la fecha de corte del reporte actual.</t>
-  </si>
-  <si>
-    <t>Corresponde a aquellos EE que presentan al menos 1 vacante disponible y 1 estudiante en lista de espera en cualquier nivel, y que por falta de gestión no se ha asignado dicha vacante.</t>
-  </si>
-  <si>
     <t>Días sin movimiento:</t>
   </si>
   <si>
     <t>Vacantes sin asignar:</t>
+  </si>
+  <si>
+    <t>Cantidad de estudiantes que no se les ha asignado una vacante aún cuando dicha vacante se encuentra disponible.</t>
+  </si>
+  <si>
+    <t>Cantidad de días transcurridos desde la última asignación de vacantes hasta la fecha de corte del reporte actual.</t>
+  </si>
+  <si>
+    <t>Cantidad de EE que presentan al menos 1 vacante disponible y 1 estudiante en lista de espera en cualquier nivel.</t>
   </si>
 </sst>
 </file>
@@ -379,13 +379,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B5"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="26.140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="48.85546875" customWidth="1"/>
+    <col min="1" max="1" width="26.1796875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="48.81640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -393,15 +393,15 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="60" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" ht="29" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
         <v>3</v>
       </c>
@@ -409,23 +409,294 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="45" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B4" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A5" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="5" spans="1:2" ht="45" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
+      <c r="B5" s="2" t="s">
         <v>8</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>6</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x0101006B669D009E7E504AA684E90EBF711B5E" ma:contentTypeVersion="14" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="b6e6a595bf14e48cece100bd18eb1a9b">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="afbb1349-6f11-4e73-acee-9bf531c9a2c9" xmlns:ns3="0df364dd-6eea-4d69-a0dc-659079815eaa" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="cb543e27a40002b0ba242570387ed2f7" ns2:_="" ns3:_="">
+    <xsd:import namespace="afbb1349-6f11-4e73-acee-9bf531c9a2c9"/>
+    <xsd:import namespace="0df364dd-6eea-4d69-a0dc-659079815eaa"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
+                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
+                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceBillingMetadata" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="afbb1349-6f11-4e73-acee-9bf531c9a2c9" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="10" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="11" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceDateTaken" ma:index="12" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceGenerationTime" ma:index="13" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceEventHashCode" ma:index="14" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaLengthInSeconds" ma:index="15" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Unknown"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="17" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Etiquetas de imagen" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="7537f579-4ce9-49fd-8c78-a6489e1e012c" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="MediaServiceLocation" ma:index="19" nillable="true" ma:displayName="Location" ma:indexed="true" ma:internalName="MediaServiceLocation" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceOCR" ma:index="20" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceBillingMetadata" ma:index="21" nillable="true" ma:displayName="MediaServiceBillingMetadata" ma:hidden="true" ma:internalName="MediaServiceBillingMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="0df364dd-6eea-4d69-a0dc-659079815eaa" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="TaxCatchAll" ma:index="18" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{0acb6d9d-5e5c-4c9f-b01d-8060abc34fef}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="0df364dd-6eea-4d69-a0dc-659079815eaa">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:MultiChoiceLookup">
+            <xsd:sequence>
+              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Tipo de contenido"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Título"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="afbb1349-6f11-4e73-acee-9bf531c9a2c9">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="0df364dd-6eea-4d69-a0dc-659079815eaa" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7F961298-0F43-49AC-B926-7A583243B5FB}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="afbb1349-6f11-4e73-acee-9bf531c9a2c9"/>
+    <ds:schemaRef ds:uri="0df364dd-6eea-4d69-a0dc-659079815eaa"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{160E865B-3AD5-4EEE-B81F-BB575D87F9EC}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="afbb1349-6f11-4e73-acee-9bf531c9a2c9"/>
+    <ds:schemaRef ds:uri="0df364dd-6eea-4d69-a0dc-659079815eaa"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{23B7320D-F52A-498B-8291-9ED69CD7FEF9}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>